--- a/manuscript/submission_data/source_data/Source_Data_Supplementary_Figure_3.xlsx
+++ b/manuscript/submission_data/source_data/Source_Data_Supplementary_Figure_3.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Panel_A" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Panel_B" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Panel_C" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Panel_A" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Panel_B" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Panel_C" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU61"/>
+  <dimension ref="A1:AU63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -654,12 +654,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>prn_evt_insufficient__not_available_current_step3</t>
+          <t>prn_evt_fragmented_contigs</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>insufficient_data</t>
+          <t>uncertain_fragmented_assembly</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1181,12 +1181,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>prn_evt_insufficient__not_available_current_step3</t>
+          <t>prn_evt_fragmented_contigs</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>insufficient_data</t>
+          <t>uncertain_fragmented_assembly</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>319</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>105</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>58</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1614,17 +1614,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>prn_evt_insufficient__not_available_current_step3</t>
+          <t>prn_evt_fragmented_contigs</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>insufficient_data</t>
+          <t>uncertain_fragmented_assembly</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1782,17 +1782,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>prn_evt_other_disruption__insertion_like__gap1040</t>
+          <t>prn_evt_insufficient__partial</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>coding_disrupted_other</t>
+          <t>insufficient_data</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1819,12 +1819,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>prn_evt_rearrangement__within_contig__cov94</t>
+          <t>prn_evt_other_disruption__insertion_like__gap1040</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>coding_disrupted_inversion_or_rearrangement</t>
+          <t>coding_disrupted_other</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1848,435 +1848,311 @@
         </is>
       </c>
     </row>
-    <row r="39"/>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>prn_evt_rearrangement__within_contig__cov66</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>coding_disrupted_inversion_or_rearrangement</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
     <row r="40"/>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr">
+    <row r="41"/>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
         <is>
           <t>source_file</t>
         </is>
       </c>
-      <c r="B41" s="1" t="inlineStr">
+      <c r="B42" s="1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t>manuscript/figure_data/selected_country/selected_country_origin_package_summary.tsv</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>found</t>
         </is>
       </c>
     </row>
-    <row r="43"/>
-    <row r="44">
-      <c r="A44" s="1" t="inlineStr">
+    <row r="44"/>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
         <is>
           <t>origin_id</t>
         </is>
       </c>
-      <c r="B44" s="1" t="inlineStr">
+      <c r="B45" s="1" t="inlineStr">
         <is>
           <t>analysis_source</t>
         </is>
       </c>
-      <c r="C44" s="1" t="inlineStr">
+      <c r="C45" s="1" t="inlineStr">
         <is>
           <t>n_disrupted_descendants</t>
         </is>
       </c>
-      <c r="D44" s="1" t="inlineStr">
+      <c r="D45" s="1" t="inlineStr">
         <is>
           <t>n_total_descendants</t>
         </is>
       </c>
-      <c r="E44" s="1" t="inlineStr">
+      <c r="E45" s="1" t="inlineStr">
         <is>
           <t>follow_up_years</t>
         </is>
       </c>
-      <c r="F44" s="1" t="inlineStr">
+      <c r="F45" s="1" t="inlineStr">
         <is>
           <t>origin_country_iso3</t>
         </is>
       </c>
-      <c r="G44" s="1" t="inlineStr">
+      <c r="G45" s="1" t="inlineStr">
         <is>
           <t>origin_year</t>
         </is>
       </c>
-      <c r="H44" s="1" t="inlineStr">
+      <c r="H45" s="1" t="inlineStr">
         <is>
           <t>last_year</t>
         </is>
       </c>
-      <c r="I44" s="1" t="inlineStr">
+      <c r="I45" s="1" t="inlineStr">
         <is>
           <t>mechanism_group</t>
         </is>
       </c>
-      <c r="J44" s="1" t="inlineStr">
+      <c r="J45" s="1" t="inlineStr">
         <is>
           <t>origin_ptxP_allele</t>
         </is>
       </c>
-      <c r="K44" s="1" t="inlineStr">
+      <c r="K45" s="1" t="inlineStr">
         <is>
           <t>origin_fim2_hash</t>
         </is>
       </c>
-      <c r="L44" s="1" t="inlineStr">
+      <c r="L45" s="1" t="inlineStr">
         <is>
           <t>origin_fim3_hash</t>
         </is>
       </c>
-      <c r="M44" s="1" t="inlineStr">
+      <c r="M45" s="1" t="inlineStr">
         <is>
           <t>origin_genotype_background</t>
         </is>
       </c>
-      <c r="N44" s="1" t="inlineStr">
+      <c r="N45" s="1" t="inlineStr">
         <is>
           <t>major_lineage</t>
         </is>
       </c>
-      <c r="O44" s="1" t="inlineStr">
+      <c r="O45" s="1" t="inlineStr">
         <is>
           <t>major_lineage_source</t>
         </is>
       </c>
-      <c r="P44" s="1" t="inlineStr">
+      <c r="P45" s="1" t="inlineStr">
         <is>
           <t>major_mlst_st</t>
         </is>
       </c>
-      <c r="Q44" s="1" t="inlineStr">
+      <c r="Q45" s="1" t="inlineStr">
         <is>
           <t>major_background_profile_id</t>
         </is>
       </c>
-      <c r="R44" s="1" t="inlineStr">
+      <c r="R45" s="1" t="inlineStr">
         <is>
           <t>major_background_label</t>
         </is>
       </c>
-      <c r="S44" s="1" t="inlineStr">
+      <c r="S45" s="1" t="inlineStr">
         <is>
           <t>major_ptxP_label</t>
         </is>
       </c>
-      <c r="T44" s="1" t="inlineStr">
+      <c r="T45" s="1" t="inlineStr">
         <is>
           <t>major_fim3_label</t>
         </is>
       </c>
-      <c r="U44" s="1" t="inlineStr">
+      <c r="U45" s="1" t="inlineStr">
         <is>
           <t>major_fhaB2400_5550_label</t>
         </is>
       </c>
-      <c r="V44" s="1" t="inlineStr">
+      <c r="V45" s="1" t="inlineStr">
         <is>
           <t>major_23s_status</t>
         </is>
       </c>
-      <c r="W44" s="1" t="inlineStr">
+      <c r="W45" s="1" t="inlineStr">
         <is>
           <t>macrolide_background</t>
         </is>
       </c>
-      <c r="X44" s="1" t="inlineStr">
+      <c r="X45" s="1" t="inlineStr">
         <is>
           <t>vaccine_environment</t>
         </is>
       </c>
-      <c r="Y44" s="1" t="inlineStr">
+      <c r="Y45" s="1" t="inlineStr">
         <is>
           <t>branch_support</t>
         </is>
       </c>
-      <c r="Z44" s="1" t="inlineStr">
+      <c r="Z45" s="1" t="inlineStr">
         <is>
           <t>origin_support_score</t>
         </is>
       </c>
-      <c r="AA44" s="1" t="inlineStr">
+      <c r="AA45" s="1" t="inlineStr">
         <is>
           <t>origin_confidence</t>
         </is>
       </c>
-      <c r="AB44" s="1" t="inlineStr">
+      <c r="AB45" s="1" t="inlineStr">
         <is>
           <t>established_ge3_descendants</t>
         </is>
       </c>
-      <c r="AC44" s="1" t="inlineStr">
+      <c r="AC45" s="1" t="inlineStr">
         <is>
           <t>established_ge2_followup_years</t>
         </is>
       </c>
-      <c r="AD44" s="1" t="inlineStr">
+      <c r="AD45" s="1" t="inlineStr">
         <is>
           <t>dominant_prn_mechanism</t>
         </is>
       </c>
-      <c r="AE44" s="1" t="inlineStr">
+      <c r="AE45" s="1" t="inlineStr">
         <is>
           <t>pastml_support_consistent</t>
         </is>
       </c>
-      <c r="AF44" s="1" t="inlineStr">
+      <c r="AF45" s="1" t="inlineStr">
         <is>
           <t>origin_ptxP_like</t>
         </is>
       </c>
-      <c r="AG44" s="1" t="inlineStr">
+      <c r="AG45" s="1" t="inlineStr">
         <is>
           <t>origin_fim2_present</t>
         </is>
       </c>
-      <c r="AH44" s="1" t="inlineStr">
+      <c r="AH45" s="1" t="inlineStr">
         <is>
           <t>origin_fim3_present</t>
         </is>
       </c>
-      <c r="AI44" s="1" t="inlineStr">
+      <c r="AI45" s="1" t="inlineStr">
         <is>
           <t>origin_mr_dominant</t>
         </is>
       </c>
-      <c r="AJ44" s="1" t="inlineStr">
+      <c r="AJ45" s="1" t="inlineStr">
         <is>
           <t>combined_hitchhiker_signature</t>
         </is>
       </c>
-      <c r="AK44" s="1" t="inlineStr">
+      <c r="AK45" s="1" t="inlineStr">
         <is>
           <t>background_signature</t>
         </is>
       </c>
-      <c r="AL44" s="1" t="inlineStr">
+      <c r="AL45" s="1" t="inlineStr">
         <is>
           <t>package_country_iso3</t>
         </is>
       </c>
-      <c r="AM44" s="1" t="inlineStr">
+      <c r="AM45" s="1" t="inlineStr">
         <is>
           <t>local_origin_consistency_status</t>
         </is>
       </c>
-      <c r="AN44" s="1" t="inlineStr">
+      <c r="AN45" s="1" t="inlineStr">
         <is>
           <t>preserves_single_origin_consistent_package</t>
         </is>
       </c>
-      <c r="AO44" s="1" t="inlineStr">
+      <c r="AO45" s="1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="AP44" s="1" t="inlineStr">
+      <c r="AP45" s="1" t="inlineStr">
         <is>
           <t>tree_representative_validation_level</t>
         </is>
       </c>
-      <c r="AQ44" s="1" t="inlineStr">
+      <c r="AQ45" s="1" t="inlineStr">
         <is>
           <t>representative_validation_level</t>
         </is>
       </c>
-      <c r="AR44" s="1" t="inlineStr">
+      <c r="AR45" s="1" t="inlineStr">
         <is>
           <t>origin_package_hard_anchor</t>
         </is>
       </c>
-      <c r="AS44" s="1" t="inlineStr">
+      <c r="AS45" s="1" t="inlineStr">
         <is>
           <t>dominant_event_hard_anchor</t>
         </is>
       </c>
-      <c r="AT44" s="1" t="inlineStr">
+      <c r="AT45" s="1" t="inlineStr">
         <is>
           <t>dominant_prn_event_id</t>
         </is>
       </c>
-      <c r="AU44" s="1" t="inlineStr">
+      <c r="AU45" s="1" t="inlineStr">
         <is>
           <t>dominant_event_validation_level</t>
         </is>
       </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>origin_0019</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>support_filtered_fitch</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>NZL</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>2012.0</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>2017.0</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>IS481</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>ptxP_3</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>f42558239a68e014b1b3707b0dfb5fd2</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>f42558239a68e014b1b3707b0dfb5fd2</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>ptxP3/PRN-</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="inlineStr"/>
-      <c r="S45" t="inlineStr"/>
-      <c r="T45" t="inlineStr"/>
-      <c r="U45" t="inlineStr"/>
-      <c r="V45" t="inlineStr"/>
-      <c r="W45" t="inlineStr">
-        <is>
-          <t>not_MR_A2047G_dominant</t>
-        </is>
-      </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>routine_ap_prn_positive</t>
-        </is>
-      </c>
-      <c r="Y45" t="inlineStr">
-        <is>
-          <t>98.0</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AA45" t="inlineStr"/>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD45" t="inlineStr">
-        <is>
-          <t>coding_disrupted_is481</t>
-        </is>
-      </c>
-      <c r="AE45" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AF45" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AG45" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>ptxP3|fim3_present|fhaB2400_5550_unassigned|not_MR_A2047G_dominant|routine_ap_prn_positive</t>
-        </is>
-      </c>
-      <c r="AL45" t="inlineStr"/>
-      <c r="AM45" t="inlineStr"/>
-      <c r="AN45" t="inlineStr"/>
-      <c r="AO45" t="inlineStr"/>
-      <c r="AP45" t="inlineStr"/>
-      <c r="AQ45" t="inlineStr"/>
-      <c r="AR45" t="inlineStr"/>
-      <c r="AS45" t="inlineStr"/>
-      <c r="AT45" t="inlineStr"/>
-      <c r="AU45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>origin_0020</t>
+          <t>origin_0019</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2341,11 +2217,7 @@
       </c>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr"/>
@@ -2364,7 +2236,7 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
@@ -2437,7 +2309,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>origin_0018</t>
+          <t>origin_0020</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2447,32 +2319,32 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>NZL</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2010.0</t>
+          <t>2012.0</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2020.0</t>
+          <t>2017.0</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2502,11 +2374,7 @@
       </c>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr"/>
@@ -2525,12 +2393,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>0.96904</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr"/>
@@ -2598,7 +2466,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>origin_0015</t>
+          <t>origin_0018</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2608,17 +2476,17 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>322</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>323</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2628,12 +2496,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2011.0</t>
+          <t>2010.0</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2019.0</t>
+          <t>2020.0</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2663,11 +2531,7 @@
       </c>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr"/>
@@ -2686,12 +2550,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>0.975</t>
+          <t>0.944272</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr"/>
@@ -2759,7 +2623,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>origin_0002</t>
+          <t>origin_0013</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2769,17 +2633,17 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2789,12 +2653,12 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2012.0</t>
+          <t>2011.0</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2018.0</t>
+          <t>2014.0</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2824,11 +2688,7 @@
       </c>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr"/>
@@ -2852,7 +2712,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.833333</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr"/>
@@ -2910,41 +2770,17 @@
       <c r="AM49" t="inlineStr"/>
       <c r="AN49" t="inlineStr"/>
       <c r="AO49" t="inlineStr"/>
-      <c r="AP49" t="inlineStr">
-        <is>
-          <t>read_backed_supported</t>
-        </is>
-      </c>
-      <c r="AQ49" t="inlineStr">
-        <is>
-          <t>read_backed_supported</t>
-        </is>
-      </c>
-      <c r="AR49" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AS49" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AT49" t="inlineStr">
-        <is>
-          <t>prn_evt_rearrangement__within_contig__cov58</t>
-        </is>
-      </c>
-      <c r="AU49" t="inlineStr">
-        <is>
-          <t>read_backed_supported</t>
-        </is>
-      </c>
+      <c r="AP49" t="inlineStr"/>
+      <c r="AQ49" t="inlineStr"/>
+      <c r="AR49" t="inlineStr"/>
+      <c r="AS49" t="inlineStr"/>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AU49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>origin_0011</t>
+          <t>origin_0015</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2954,17 +2790,17 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>39</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2974,17 +2810,17 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2015.0</t>
+          <t>2011.0</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2020.0</t>
+          <t>2019.0</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>inversion/rearrangement</t>
+          <t>IS481</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3009,11 +2845,7 @@
       </c>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr"/>
@@ -3032,12 +2864,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>0.881356</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr"/>
@@ -3053,7 +2885,7 @@
       </c>
       <c r="AD50" t="inlineStr">
         <is>
-          <t>coding_disrupted_inversion_or_rearrangement</t>
+          <t>coding_disrupted_is481</t>
         </is>
       </c>
       <c r="AE50" t="inlineStr">
@@ -3105,7 +2937,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>origin_0005</t>
+          <t>origin_0002</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3115,17 +2947,17 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3135,12 +2967,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2016.0</t>
+          <t>2012.0</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2016.0</t>
+          <t>2018.0</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3170,11 +3002,7 @@
       </c>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr"/>
@@ -3204,12 +3032,12 @@
       <c r="AA51" t="inlineStr"/>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD51" t="inlineStr">
@@ -3256,473 +3084,529 @@
       <c r="AM51" t="inlineStr"/>
       <c r="AN51" t="inlineStr"/>
       <c r="AO51" t="inlineStr"/>
-      <c r="AP51" t="inlineStr"/>
-      <c r="AQ51" t="inlineStr"/>
-      <c r="AR51" t="inlineStr"/>
-      <c r="AS51" t="inlineStr"/>
-      <c r="AT51" t="inlineStr"/>
-      <c r="AU51" t="inlineStr"/>
-    </row>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54">
-      <c r="A54" s="1" t="inlineStr">
+      <c r="AP51" t="inlineStr">
+        <is>
+          <t>read_backed_supported</t>
+        </is>
+      </c>
+      <c r="AQ51" t="inlineStr">
+        <is>
+          <t>read_backed_supported</t>
+        </is>
+      </c>
+      <c r="AR51" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AS51" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AT51" t="inlineStr">
+        <is>
+          <t>prn_evt_rearrangement__within_contig__cov58</t>
+        </is>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
+          <t>read_backed_supported</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>origin_0010</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>support_filtered_fitch</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2015.0</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>2020.0</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>inversion/rearrangement</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>ptxP_3</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>f42558239a68e014b1b3707b0dfb5fd2</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>f42558239a68e014b1b3707b0dfb5fd2</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>ptxP3/PRN-</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>not_MR_A2047G_dominant</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>routine_ap_prn_positive</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>0.881356</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr"/>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD52" t="inlineStr">
+        <is>
+          <t>coding_disrupted_inversion_or_rearrangement</t>
+        </is>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AG52" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>ptxP3|fim3_present|fhaB2400_5550_unassigned|not_MR_A2047G_dominant|routine_ap_prn_positive</t>
+        </is>
+      </c>
+      <c r="AL52" t="inlineStr"/>
+      <c r="AM52" t="inlineStr"/>
+      <c r="AN52" t="inlineStr"/>
+      <c r="AO52" t="inlineStr"/>
+      <c r="AP52" t="inlineStr"/>
+      <c r="AQ52" t="inlineStr"/>
+      <c r="AR52" t="inlineStr"/>
+      <c r="AS52" t="inlineStr"/>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AU52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>origin_0005</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>support_filtered_fitch</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2016.0</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>2016.0</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>inversion/rearrangement</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>ptxP_3</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>f42558239a68e014b1b3707b0dfb5fd2</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>f42558239a68e014b1b3707b0dfb5fd2</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>ptxP3/PRN-</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="inlineStr"/>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr"/>
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>not_MR_A2047G_dominant</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>routine_ap_prn_positive</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr"/>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD53" t="inlineStr">
+        <is>
+          <t>coding_disrupted_inversion_or_rearrangement</t>
+        </is>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AG53" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>ptxP3|fim3_present|fhaB2400_5550_unassigned|not_MR_A2047G_dominant|routine_ap_prn_positive</t>
+        </is>
+      </c>
+      <c r="AL53" t="inlineStr"/>
+      <c r="AM53" t="inlineStr"/>
+      <c r="AN53" t="inlineStr"/>
+      <c r="AO53" t="inlineStr"/>
+      <c r="AP53" t="inlineStr"/>
+      <c r="AQ53" t="inlineStr"/>
+      <c r="AR53" t="inlineStr"/>
+      <c r="AS53" t="inlineStr"/>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AU53" t="inlineStr"/>
+    </row>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
         <is>
           <t>source_file</t>
         </is>
       </c>
-      <c r="B54" s="1" t="inlineStr">
+      <c r="B56" s="1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
+    <row r="57">
+      <c r="A57" t="inlineStr">
         <is>
           <t>manuscript/figure_data/local_rooted_package_tree_summary.tsv</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>found</t>
         </is>
       </c>
     </row>
-    <row r="56"/>
-    <row r="57">
-      <c r="A57" s="1" t="inlineStr">
+    <row r="58"/>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr">
         <is>
           <t>origin_id</t>
         </is>
       </c>
-      <c r="B57" s="1" t="inlineStr">
+      <c r="B59" s="1" t="inlineStr">
         <is>
           <t>dominant_prn_event_id</t>
         </is>
       </c>
-      <c r="C57" s="1" t="inlineStr">
+      <c r="C59" s="1" t="inlineStr">
         <is>
           <t>major_mlst_st</t>
         </is>
       </c>
-      <c r="D57" s="1" t="inlineStr">
+      <c r="D59" s="1" t="inlineStr">
         <is>
           <t>package_country_iso3</t>
         </is>
       </c>
-      <c r="E57" s="1" t="inlineStr">
+      <c r="E59" s="1" t="inlineStr">
         <is>
           <t>package_target_disrupted_tips</t>
         </is>
       </c>
-      <c r="F57" s="1" t="inlineStr">
+      <c r="F59" s="1" t="inlineStr">
         <is>
           <t>rooted_tree_selected_targets</t>
         </is>
       </c>
-      <c r="G57" s="1" t="inlineStr">
+      <c r="G59" s="1" t="inlineStr">
         <is>
           <t>rooted_tree_selected_intact_neighbors</t>
         </is>
       </c>
-      <c r="H57" s="1" t="inlineStr">
+      <c r="H59" s="1" t="inlineStr">
         <is>
           <t>proxy_extra_disrupted_targets_selected</t>
         </is>
       </c>
-      <c r="I57" s="1" t="inlineStr">
+      <c r="I59" s="1" t="inlineStr">
         <is>
           <t>proxy_selected_intact_neighbors</t>
         </is>
       </c>
-      <c r="J57" s="1" t="inlineStr">
+      <c r="J59" s="1" t="inlineStr">
         <is>
           <t>selected_total_genomes</t>
         </is>
       </c>
-      <c r="K57" s="1" t="inlineStr">
+      <c r="K59" s="1" t="inlineStr">
         <is>
           <t>completed_snippy_genomes</t>
         </is>
       </c>
-      <c r="L57" s="1" t="inlineStr">
+      <c r="L59" s="1" t="inlineStr">
         <is>
           <t>local_tip_count</t>
         </is>
       </c>
-      <c r="M57" s="1" t="inlineStr">
+      <c r="M59" s="1" t="inlineStr">
         <is>
           <t>local_disrupted_tip_count</t>
         </is>
       </c>
-      <c r="N57" s="1" t="inlineStr">
+      <c r="N59" s="1" t="inlineStr">
         <is>
           <t>local_fitch_origin_events</t>
         </is>
       </c>
-      <c r="O57" s="1" t="inlineStr">
+      <c r="O59" s="1" t="inlineStr">
         <is>
           <t>local_pastml_origin_events</t>
         </is>
       </c>
-      <c r="P57" s="1" t="inlineStr">
+      <c r="P59" s="1" t="inlineStr">
         <is>
           <t>target_package_retained_disrupted_tips</t>
         </is>
       </c>
-      <c r="Q57" s="1" t="inlineStr">
+      <c r="Q59" s="1" t="inlineStr">
         <is>
           <t>target_package_tip_retention_fraction</t>
         </is>
       </c>
-      <c r="R57" s="1" t="inlineStr">
+      <c r="R59" s="1" t="inlineStr">
         <is>
           <t>target_package_origin_partition_count</t>
         </is>
       </c>
-      <c r="S57" s="1" t="inlineStr">
+      <c r="S59" s="1" t="inlineStr">
         <is>
           <t>local_origin_consistency_status</t>
         </is>
       </c>
-      <c r="T57" s="1" t="inlineStr">
+      <c r="T59" s="1" t="inlineStr">
         <is>
           <t>preserves_single_origin_consistent_package</t>
         </is>
       </c>
-      <c r="U57" s="1" t="inlineStr">
+      <c r="U59" s="1" t="inlineStr">
         <is>
           <t>covering_local_origin_ids</t>
         </is>
       </c>
-      <c r="V57" s="1" t="inlineStr">
+      <c r="V59" s="1" t="inlineStr">
         <is>
           <t>covering_branch_supports</t>
         </is>
       </c>
-      <c r="W57" s="1" t="inlineStr">
+      <c r="W59" s="1" t="inlineStr">
         <is>
           <t>representative_covering_branch_support</t>
         </is>
       </c>
-      <c r="X57" s="1" t="inlineStr">
+      <c r="X59" s="1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="Y57" s="1" t="inlineStr">
+      <c r="Y59" s="1" t="inlineStr">
         <is>
           <t>status_detail</t>
         </is>
       </c>
-      <c r="Z57" s="1" t="inlineStr">
+      <c r="Z59" s="1" t="inlineStr">
         <is>
           <t>selection_plan</t>
         </is>
       </c>
-      <c r="AA57" s="1" t="inlineStr">
+      <c r="AA59" s="1" t="inlineStr">
         <is>
           <t>local_phylo_dir</t>
         </is>
       </c>
-      <c r="AB57" s="1" t="inlineStr">
+      <c r="AB59" s="1" t="inlineStr">
         <is>
           <t>local_asr_dir</t>
         </is>
       </c>
-      <c r="AC57" s="1" t="inlineStr">
+      <c r="AC59" s="1" t="inlineStr">
         <is>
           <t>notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>origin_0001</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>prn_evt_coding_disrupted_is481__is481__gap1043</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>FRA</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Q58" t="inlineStr">
-        <is>
-          <t>1.000000</t>
-        </is>
-      </c>
-      <c r="R58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>single_origin_consistent</t>
-        </is>
-      </c>
-      <c r="T58" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>origin_0001</t>
-        </is>
-      </c>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="W58" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Y58" t="inlineStr"/>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>pipelines/bp_step5/work/local_rooted_package_trees/origin_0001/snippy_ctg_plan.tsv</t>
-        </is>
-      </c>
-      <c r="AA58" t="inlineStr">
-        <is>
-          <t>outputs/workflow/local_rooted_package_trees/origin_0001/phylo</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>outputs/workflow/local_rooted_package_trees/origin_0001/asr</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>package_local_rooted_snp_tree_rebuilt_from_existing_snippy_outputs_then_passed_through_standard_m4_and_m5_wrappers</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>origin_0003</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>prn_evt_rearrangement__within_contig__cov58</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Q59" t="inlineStr">
-        <is>
-          <t>1.000000</t>
-        </is>
-      </c>
-      <c r="R59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>single_origin_consistent</t>
-        </is>
-      </c>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>origin_0001</t>
-        </is>
-      </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="W59" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Y59" t="inlineStr"/>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>pipelines/bp_step5/work/local_rooted_package_trees/origin_0003/snippy_ctg_plan.tsv</t>
-        </is>
-      </c>
-      <c r="AA59" t="inlineStr">
-        <is>
-          <t>outputs/workflow/local_rooted_package_trees/origin_0003/phylo</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>outputs/workflow/local_rooted_package_trees/origin_0003/asr</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>package_local_rooted_snp_tree_rebuilt_from_existing_snippy_outputs_then_passed_through_standard_m4_and_m5_wrappers</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>origin_0007</t>
+          <t>origin_0001</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3737,7 +3621,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -3762,22 +3646,22 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>18</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -3787,12 +3671,12 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -3843,17 +3727,17 @@
       <c r="Y60" t="inlineStr"/>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>pipelines/bp_step5/work/local_rooted_package_trees/origin_0007/snippy_ctg_plan.tsv</t>
+          <t>pipelines/bp_step5/work/local_rooted_package_trees/origin_0001/snippy_ctg_plan.tsv</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>outputs/workflow/local_rooted_package_trees/origin_0007/phylo</t>
+          <t>outputs/workflow/local_rooted_package_trees/origin_0001/phylo</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>outputs/workflow/local_rooted_package_trees/origin_0007/asr</t>
+          <t>outputs/workflow/local_rooted_package_trees/origin_0001/asr</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
@@ -3865,112 +3749,108 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>origin_0008</t>
+          <t>origin_0003</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>prn_evt_coding_disrupted_is481__is481__gap1043</t>
+          <t>prn_evt_rearrangement__within_contig__cov58</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>0.157895</t>
+          <t>1.000000</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>split_across_multiple_local_origins</t>
+          <t>single_origin_consistent</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>origin_0001;origin_0003</t>
+          <t>origin_0001</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>NA;85</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="W61" t="inlineStr">
@@ -3986,20 +3866,306 @@
       <c r="Y61" t="inlineStr"/>
       <c r="Z61" t="inlineStr">
         <is>
+          <t>pipelines/bp_step5/work/local_rooted_package_trees/origin_0003/snippy_ctg_plan.tsv</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>outputs/workflow/local_rooted_package_trees/origin_0003/phylo</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>outputs/workflow/local_rooted_package_trees/origin_0003/asr</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>package_local_rooted_snp_tree_rebuilt_from_existing_snippy_outputs_then_passed_through_standard_m4_and_m5_wrappers</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>origin_0007</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>prn_evt_coding_disrupted_is481__is481__gap1043</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>1.000000</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>single_origin_consistent</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>origin_0001</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr"/>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>pipelines/bp_step5/work/local_rooted_package_trees/origin_0007/snippy_ctg_plan.tsv</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>outputs/workflow/local_rooted_package_trees/origin_0007/phylo</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>outputs/workflow/local_rooted_package_trees/origin_0007/asr</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>package_local_rooted_snp_tree_rebuilt_from_existing_snippy_outputs_then_passed_through_standard_m4_and_m5_wrappers</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>origin_0008</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>prn_evt_coding_disrupted_is481__is481__gap1043</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>0.157895</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>split_across_multiple_local_origins</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>origin_0001;origin_0003</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>NA;85</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr"/>
+      <c r="Z63" t="inlineStr">
+        <is>
           <t>pipelines/bp_step5/work/local_rooted_package_trees/origin_0008/snippy_ctg_plan.tsv</t>
         </is>
       </c>
-      <c r="AA61" t="inlineStr">
+      <c r="AA63" t="inlineStr">
         <is>
           <t>outputs/workflow/local_rooted_package_trees/origin_0008/phylo</t>
         </is>
       </c>
-      <c r="AB61" t="inlineStr">
+      <c r="AB63" t="inlineStr">
         <is>
           <t>outputs/workflow/local_rooted_package_trees/origin_0008/asr</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
+      <c r="AC63" t="inlineStr">
         <is>
           <t>package_local_rooted_snp_tree_rebuilt_from_existing_snippy_outputs_then_passed_through_standard_m4_and_m5_wrappers</t>
         </is>
@@ -4016,7 +4182,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU61"/>
+  <dimension ref="A1:AU63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -4243,12 +4409,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>prn_evt_insufficient__not_available_current_step3</t>
+          <t>prn_evt_fragmented_contigs</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>insufficient_data</t>
+          <t>uncertain_fragmented_assembly</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -4770,12 +4936,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>prn_evt_insufficient__not_available_current_step3</t>
+          <t>prn_evt_fragmented_contigs</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>insufficient_data</t>
+          <t>uncertain_fragmented_assembly</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5062,7 +5228,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>319</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -5119,7 +5285,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>105</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -5176,7 +5342,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>58</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -5203,17 +5369,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>prn_evt_insufficient__not_available_current_step3</t>
+          <t>prn_evt_fragmented_contigs</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>insufficient_data</t>
+          <t>uncertain_fragmented_assembly</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -5287,7 +5453,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -5371,17 +5537,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>prn_evt_other_disruption__insertion_like__gap1040</t>
+          <t>prn_evt_insufficient__partial</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>coding_disrupted_other</t>
+          <t>insufficient_data</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -5408,12 +5574,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>prn_evt_rearrangement__within_contig__cov94</t>
+          <t>prn_evt_other_disruption__insertion_like__gap1040</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>coding_disrupted_inversion_or_rearrangement</t>
+          <t>coding_disrupted_other</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5437,435 +5603,311 @@
         </is>
       </c>
     </row>
-    <row r="39"/>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>prn_evt_rearrangement__within_contig__cov66</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>coding_disrupted_inversion_or_rearrangement</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
     <row r="40"/>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr">
+    <row r="41"/>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
         <is>
           <t>source_file</t>
         </is>
       </c>
-      <c r="B41" s="1" t="inlineStr">
+      <c r="B42" s="1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t>manuscript/figure_data/selected_country/selected_country_origin_package_summary.tsv</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>found</t>
         </is>
       </c>
     </row>
-    <row r="43"/>
-    <row r="44">
-      <c r="A44" s="1" t="inlineStr">
+    <row r="44"/>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
         <is>
           <t>origin_id</t>
         </is>
       </c>
-      <c r="B44" s="1" t="inlineStr">
+      <c r="B45" s="1" t="inlineStr">
         <is>
           <t>analysis_source</t>
         </is>
       </c>
-      <c r="C44" s="1" t="inlineStr">
+      <c r="C45" s="1" t="inlineStr">
         <is>
           <t>n_disrupted_descendants</t>
         </is>
       </c>
-      <c r="D44" s="1" t="inlineStr">
+      <c r="D45" s="1" t="inlineStr">
         <is>
           <t>n_total_descendants</t>
         </is>
       </c>
-      <c r="E44" s="1" t="inlineStr">
+      <c r="E45" s="1" t="inlineStr">
         <is>
           <t>follow_up_years</t>
         </is>
       </c>
-      <c r="F44" s="1" t="inlineStr">
+      <c r="F45" s="1" t="inlineStr">
         <is>
           <t>origin_country_iso3</t>
         </is>
       </c>
-      <c r="G44" s="1" t="inlineStr">
+      <c r="G45" s="1" t="inlineStr">
         <is>
           <t>origin_year</t>
         </is>
       </c>
-      <c r="H44" s="1" t="inlineStr">
+      <c r="H45" s="1" t="inlineStr">
         <is>
           <t>last_year</t>
         </is>
       </c>
-      <c r="I44" s="1" t="inlineStr">
+      <c r="I45" s="1" t="inlineStr">
         <is>
           <t>mechanism_group</t>
         </is>
       </c>
-      <c r="J44" s="1" t="inlineStr">
+      <c r="J45" s="1" t="inlineStr">
         <is>
           <t>origin_ptxP_allele</t>
         </is>
       </c>
-      <c r="K44" s="1" t="inlineStr">
+      <c r="K45" s="1" t="inlineStr">
         <is>
           <t>origin_fim2_hash</t>
         </is>
       </c>
-      <c r="L44" s="1" t="inlineStr">
+      <c r="L45" s="1" t="inlineStr">
         <is>
           <t>origin_fim3_hash</t>
         </is>
       </c>
-      <c r="M44" s="1" t="inlineStr">
+      <c r="M45" s="1" t="inlineStr">
         <is>
           <t>origin_genotype_background</t>
         </is>
       </c>
-      <c r="N44" s="1" t="inlineStr">
+      <c r="N45" s="1" t="inlineStr">
         <is>
           <t>major_lineage</t>
         </is>
       </c>
-      <c r="O44" s="1" t="inlineStr">
+      <c r="O45" s="1" t="inlineStr">
         <is>
           <t>major_lineage_source</t>
         </is>
       </c>
-      <c r="P44" s="1" t="inlineStr">
+      <c r="P45" s="1" t="inlineStr">
         <is>
           <t>major_mlst_st</t>
         </is>
       </c>
-      <c r="Q44" s="1" t="inlineStr">
+      <c r="Q45" s="1" t="inlineStr">
         <is>
           <t>major_background_profile_id</t>
         </is>
       </c>
-      <c r="R44" s="1" t="inlineStr">
+      <c r="R45" s="1" t="inlineStr">
         <is>
           <t>major_background_label</t>
         </is>
       </c>
-      <c r="S44" s="1" t="inlineStr">
+      <c r="S45" s="1" t="inlineStr">
         <is>
           <t>major_ptxP_label</t>
         </is>
       </c>
-      <c r="T44" s="1" t="inlineStr">
+      <c r="T45" s="1" t="inlineStr">
         <is>
           <t>major_fim3_label</t>
         </is>
       </c>
-      <c r="U44" s="1" t="inlineStr">
+      <c r="U45" s="1" t="inlineStr">
         <is>
           <t>major_fhaB2400_5550_label</t>
         </is>
       </c>
-      <c r="V44" s="1" t="inlineStr">
+      <c r="V45" s="1" t="inlineStr">
         <is>
           <t>major_23s_status</t>
         </is>
       </c>
-      <c r="W44" s="1" t="inlineStr">
+      <c r="W45" s="1" t="inlineStr">
         <is>
           <t>macrolide_background</t>
         </is>
       </c>
-      <c r="X44" s="1" t="inlineStr">
+      <c r="X45" s="1" t="inlineStr">
         <is>
           <t>vaccine_environment</t>
         </is>
       </c>
-      <c r="Y44" s="1" t="inlineStr">
+      <c r="Y45" s="1" t="inlineStr">
         <is>
           <t>branch_support</t>
         </is>
       </c>
-      <c r="Z44" s="1" t="inlineStr">
+      <c r="Z45" s="1" t="inlineStr">
         <is>
           <t>origin_support_score</t>
         </is>
       </c>
-      <c r="AA44" s="1" t="inlineStr">
+      <c r="AA45" s="1" t="inlineStr">
         <is>
           <t>origin_confidence</t>
         </is>
       </c>
-      <c r="AB44" s="1" t="inlineStr">
+      <c r="AB45" s="1" t="inlineStr">
         <is>
           <t>established_ge3_descendants</t>
         </is>
       </c>
-      <c r="AC44" s="1" t="inlineStr">
+      <c r="AC45" s="1" t="inlineStr">
         <is>
           <t>established_ge2_followup_years</t>
         </is>
       </c>
-      <c r="AD44" s="1" t="inlineStr">
+      <c r="AD45" s="1" t="inlineStr">
         <is>
           <t>dominant_prn_mechanism</t>
         </is>
       </c>
-      <c r="AE44" s="1" t="inlineStr">
+      <c r="AE45" s="1" t="inlineStr">
         <is>
           <t>pastml_support_consistent</t>
         </is>
       </c>
-      <c r="AF44" s="1" t="inlineStr">
+      <c r="AF45" s="1" t="inlineStr">
         <is>
           <t>origin_ptxP_like</t>
         </is>
       </c>
-      <c r="AG44" s="1" t="inlineStr">
+      <c r="AG45" s="1" t="inlineStr">
         <is>
           <t>origin_fim2_present</t>
         </is>
       </c>
-      <c r="AH44" s="1" t="inlineStr">
+      <c r="AH45" s="1" t="inlineStr">
         <is>
           <t>origin_fim3_present</t>
         </is>
       </c>
-      <c r="AI44" s="1" t="inlineStr">
+      <c r="AI45" s="1" t="inlineStr">
         <is>
           <t>origin_mr_dominant</t>
         </is>
       </c>
-      <c r="AJ44" s="1" t="inlineStr">
+      <c r="AJ45" s="1" t="inlineStr">
         <is>
           <t>combined_hitchhiker_signature</t>
         </is>
       </c>
-      <c r="AK44" s="1" t="inlineStr">
+      <c r="AK45" s="1" t="inlineStr">
         <is>
           <t>background_signature</t>
         </is>
       </c>
-      <c r="AL44" s="1" t="inlineStr">
+      <c r="AL45" s="1" t="inlineStr">
         <is>
           <t>package_country_iso3</t>
         </is>
       </c>
-      <c r="AM44" s="1" t="inlineStr">
+      <c r="AM45" s="1" t="inlineStr">
         <is>
           <t>local_origin_consistency_status</t>
         </is>
       </c>
-      <c r="AN44" s="1" t="inlineStr">
+      <c r="AN45" s="1" t="inlineStr">
         <is>
           <t>preserves_single_origin_consistent_package</t>
         </is>
       </c>
-      <c r="AO44" s="1" t="inlineStr">
+      <c r="AO45" s="1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="AP44" s="1" t="inlineStr">
+      <c r="AP45" s="1" t="inlineStr">
         <is>
           <t>tree_representative_validation_level</t>
         </is>
       </c>
-      <c r="AQ44" s="1" t="inlineStr">
+      <c r="AQ45" s="1" t="inlineStr">
         <is>
           <t>representative_validation_level</t>
         </is>
       </c>
-      <c r="AR44" s="1" t="inlineStr">
+      <c r="AR45" s="1" t="inlineStr">
         <is>
           <t>origin_package_hard_anchor</t>
         </is>
       </c>
-      <c r="AS44" s="1" t="inlineStr">
+      <c r="AS45" s="1" t="inlineStr">
         <is>
           <t>dominant_event_hard_anchor</t>
         </is>
       </c>
-      <c r="AT44" s="1" t="inlineStr">
+      <c r="AT45" s="1" t="inlineStr">
         <is>
           <t>dominant_prn_event_id</t>
         </is>
       </c>
-      <c r="AU44" s="1" t="inlineStr">
+      <c r="AU45" s="1" t="inlineStr">
         <is>
           <t>dominant_event_validation_level</t>
         </is>
       </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>origin_0019</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>support_filtered_fitch</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>NZL</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>2012.0</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>2017.0</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>IS481</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>ptxP_3</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>f42558239a68e014b1b3707b0dfb5fd2</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>f42558239a68e014b1b3707b0dfb5fd2</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>ptxP3/PRN-</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="inlineStr"/>
-      <c r="S45" t="inlineStr"/>
-      <c r="T45" t="inlineStr"/>
-      <c r="U45" t="inlineStr"/>
-      <c r="V45" t="inlineStr"/>
-      <c r="W45" t="inlineStr">
-        <is>
-          <t>not_MR_A2047G_dominant</t>
-        </is>
-      </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>routine_ap_prn_positive</t>
-        </is>
-      </c>
-      <c r="Y45" t="inlineStr">
-        <is>
-          <t>98.0</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AA45" t="inlineStr"/>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD45" t="inlineStr">
-        <is>
-          <t>coding_disrupted_is481</t>
-        </is>
-      </c>
-      <c r="AE45" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AF45" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AG45" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>ptxP3|fim3_present|fhaB2400_5550_unassigned|not_MR_A2047G_dominant|routine_ap_prn_positive</t>
-        </is>
-      </c>
-      <c r="AL45" t="inlineStr"/>
-      <c r="AM45" t="inlineStr"/>
-      <c r="AN45" t="inlineStr"/>
-      <c r="AO45" t="inlineStr"/>
-      <c r="AP45" t="inlineStr"/>
-      <c r="AQ45" t="inlineStr"/>
-      <c r="AR45" t="inlineStr"/>
-      <c r="AS45" t="inlineStr"/>
-      <c r="AT45" t="inlineStr"/>
-      <c r="AU45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>origin_0020</t>
+          <t>origin_0019</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5930,11 +5972,7 @@
       </c>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr"/>
@@ -5953,7 +5991,7 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
@@ -6026,7 +6064,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>origin_0018</t>
+          <t>origin_0020</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -6036,32 +6074,32 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>NZL</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2010.0</t>
+          <t>2012.0</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2020.0</t>
+          <t>2017.0</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -6091,11 +6129,7 @@
       </c>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr"/>
@@ -6114,12 +6148,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>0.96904</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr"/>
@@ -6187,7 +6221,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>origin_0015</t>
+          <t>origin_0018</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -6197,17 +6231,17 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>322</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>323</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -6217,12 +6251,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2011.0</t>
+          <t>2010.0</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2019.0</t>
+          <t>2020.0</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -6252,11 +6286,7 @@
       </c>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr"/>
@@ -6275,12 +6305,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>0.975</t>
+          <t>0.944272</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr"/>
@@ -6348,7 +6378,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>origin_0002</t>
+          <t>origin_0013</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6358,17 +6388,17 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -6378,12 +6408,12 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2012.0</t>
+          <t>2011.0</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2018.0</t>
+          <t>2014.0</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -6413,11 +6443,7 @@
       </c>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr"/>
@@ -6441,7 +6467,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.833333</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr"/>
@@ -6499,41 +6525,17 @@
       <c r="AM49" t="inlineStr"/>
       <c r="AN49" t="inlineStr"/>
       <c r="AO49" t="inlineStr"/>
-      <c r="AP49" t="inlineStr">
-        <is>
-          <t>read_backed_supported</t>
-        </is>
-      </c>
-      <c r="AQ49" t="inlineStr">
-        <is>
-          <t>read_backed_supported</t>
-        </is>
-      </c>
-      <c r="AR49" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AS49" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AT49" t="inlineStr">
-        <is>
-          <t>prn_evt_rearrangement__within_contig__cov58</t>
-        </is>
-      </c>
-      <c r="AU49" t="inlineStr">
-        <is>
-          <t>read_backed_supported</t>
-        </is>
-      </c>
+      <c r="AP49" t="inlineStr"/>
+      <c r="AQ49" t="inlineStr"/>
+      <c r="AR49" t="inlineStr"/>
+      <c r="AS49" t="inlineStr"/>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AU49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>origin_0011</t>
+          <t>origin_0015</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6543,17 +6545,17 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>39</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -6563,17 +6565,17 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2015.0</t>
+          <t>2011.0</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2020.0</t>
+          <t>2019.0</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>inversion/rearrangement</t>
+          <t>IS481</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6598,11 +6600,7 @@
       </c>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr"/>
@@ -6621,12 +6619,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>0.881356</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr"/>
@@ -6642,7 +6640,7 @@
       </c>
       <c r="AD50" t="inlineStr">
         <is>
-          <t>coding_disrupted_inversion_or_rearrangement</t>
+          <t>coding_disrupted_is481</t>
         </is>
       </c>
       <c r="AE50" t="inlineStr">
@@ -6694,7 +6692,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>origin_0005</t>
+          <t>origin_0002</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6704,17 +6702,17 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -6724,12 +6722,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2016.0</t>
+          <t>2012.0</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2016.0</t>
+          <t>2018.0</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -6759,11 +6757,7 @@
       </c>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr"/>
@@ -6793,12 +6787,12 @@
       <c r="AA51" t="inlineStr"/>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD51" t="inlineStr">
@@ -6845,473 +6839,529 @@
       <c r="AM51" t="inlineStr"/>
       <c r="AN51" t="inlineStr"/>
       <c r="AO51" t="inlineStr"/>
-      <c r="AP51" t="inlineStr"/>
-      <c r="AQ51" t="inlineStr"/>
-      <c r="AR51" t="inlineStr"/>
-      <c r="AS51" t="inlineStr"/>
-      <c r="AT51" t="inlineStr"/>
-      <c r="AU51" t="inlineStr"/>
-    </row>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54">
-      <c r="A54" s="1" t="inlineStr">
+      <c r="AP51" t="inlineStr">
+        <is>
+          <t>read_backed_supported</t>
+        </is>
+      </c>
+      <c r="AQ51" t="inlineStr">
+        <is>
+          <t>read_backed_supported</t>
+        </is>
+      </c>
+      <c r="AR51" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AS51" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AT51" t="inlineStr">
+        <is>
+          <t>prn_evt_rearrangement__within_contig__cov58</t>
+        </is>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
+          <t>read_backed_supported</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>origin_0010</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>support_filtered_fitch</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2015.0</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>2020.0</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>inversion/rearrangement</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>ptxP_3</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>f42558239a68e014b1b3707b0dfb5fd2</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>f42558239a68e014b1b3707b0dfb5fd2</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>ptxP3/PRN-</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>not_MR_A2047G_dominant</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>routine_ap_prn_positive</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>0.881356</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr"/>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD52" t="inlineStr">
+        <is>
+          <t>coding_disrupted_inversion_or_rearrangement</t>
+        </is>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AG52" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>ptxP3|fim3_present|fhaB2400_5550_unassigned|not_MR_A2047G_dominant|routine_ap_prn_positive</t>
+        </is>
+      </c>
+      <c r="AL52" t="inlineStr"/>
+      <c r="AM52" t="inlineStr"/>
+      <c r="AN52" t="inlineStr"/>
+      <c r="AO52" t="inlineStr"/>
+      <c r="AP52" t="inlineStr"/>
+      <c r="AQ52" t="inlineStr"/>
+      <c r="AR52" t="inlineStr"/>
+      <c r="AS52" t="inlineStr"/>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AU52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>origin_0005</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>support_filtered_fitch</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2016.0</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>2016.0</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>inversion/rearrangement</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>ptxP_3</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>f42558239a68e014b1b3707b0dfb5fd2</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>f42558239a68e014b1b3707b0dfb5fd2</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>ptxP3/PRN-</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="inlineStr"/>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr"/>
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>not_MR_A2047G_dominant</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>routine_ap_prn_positive</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr"/>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD53" t="inlineStr">
+        <is>
+          <t>coding_disrupted_inversion_or_rearrangement</t>
+        </is>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AG53" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>ptxP3|fim3_present|fhaB2400_5550_unassigned|not_MR_A2047G_dominant|routine_ap_prn_positive</t>
+        </is>
+      </c>
+      <c r="AL53" t="inlineStr"/>
+      <c r="AM53" t="inlineStr"/>
+      <c r="AN53" t="inlineStr"/>
+      <c r="AO53" t="inlineStr"/>
+      <c r="AP53" t="inlineStr"/>
+      <c r="AQ53" t="inlineStr"/>
+      <c r="AR53" t="inlineStr"/>
+      <c r="AS53" t="inlineStr"/>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AU53" t="inlineStr"/>
+    </row>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
         <is>
           <t>source_file</t>
         </is>
       </c>
-      <c r="B54" s="1" t="inlineStr">
+      <c r="B56" s="1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
+    <row r="57">
+      <c r="A57" t="inlineStr">
         <is>
           <t>manuscript/figure_data/local_rooted_package_tree_summary.tsv</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>found</t>
         </is>
       </c>
     </row>
-    <row r="56"/>
-    <row r="57">
-      <c r="A57" s="1" t="inlineStr">
+    <row r="58"/>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr">
         <is>
           <t>origin_id</t>
         </is>
       </c>
-      <c r="B57" s="1" t="inlineStr">
+      <c r="B59" s="1" t="inlineStr">
         <is>
           <t>dominant_prn_event_id</t>
         </is>
       </c>
-      <c r="C57" s="1" t="inlineStr">
+      <c r="C59" s="1" t="inlineStr">
         <is>
           <t>major_mlst_st</t>
         </is>
       </c>
-      <c r="D57" s="1" t="inlineStr">
+      <c r="D59" s="1" t="inlineStr">
         <is>
           <t>package_country_iso3</t>
         </is>
       </c>
-      <c r="E57" s="1" t="inlineStr">
+      <c r="E59" s="1" t="inlineStr">
         <is>
           <t>package_target_disrupted_tips</t>
         </is>
       </c>
-      <c r="F57" s="1" t="inlineStr">
+      <c r="F59" s="1" t="inlineStr">
         <is>
           <t>rooted_tree_selected_targets</t>
         </is>
       </c>
-      <c r="G57" s="1" t="inlineStr">
+      <c r="G59" s="1" t="inlineStr">
         <is>
           <t>rooted_tree_selected_intact_neighbors</t>
         </is>
       </c>
-      <c r="H57" s="1" t="inlineStr">
+      <c r="H59" s="1" t="inlineStr">
         <is>
           <t>proxy_extra_disrupted_targets_selected</t>
         </is>
       </c>
-      <c r="I57" s="1" t="inlineStr">
+      <c r="I59" s="1" t="inlineStr">
         <is>
           <t>proxy_selected_intact_neighbors</t>
         </is>
       </c>
-      <c r="J57" s="1" t="inlineStr">
+      <c r="J59" s="1" t="inlineStr">
         <is>
           <t>selected_total_genomes</t>
         </is>
       </c>
-      <c r="K57" s="1" t="inlineStr">
+      <c r="K59" s="1" t="inlineStr">
         <is>
           <t>completed_snippy_genomes</t>
         </is>
       </c>
-      <c r="L57" s="1" t="inlineStr">
+      <c r="L59" s="1" t="inlineStr">
         <is>
           <t>local_tip_count</t>
         </is>
       </c>
-      <c r="M57" s="1" t="inlineStr">
+      <c r="M59" s="1" t="inlineStr">
         <is>
           <t>local_disrupted_tip_count</t>
         </is>
       </c>
-      <c r="N57" s="1" t="inlineStr">
+      <c r="N59" s="1" t="inlineStr">
         <is>
           <t>local_fitch_origin_events</t>
         </is>
       </c>
-      <c r="O57" s="1" t="inlineStr">
+      <c r="O59" s="1" t="inlineStr">
         <is>
           <t>local_pastml_origin_events</t>
         </is>
       </c>
-      <c r="P57" s="1" t="inlineStr">
+      <c r="P59" s="1" t="inlineStr">
         <is>
           <t>target_package_retained_disrupted_tips</t>
         </is>
       </c>
-      <c r="Q57" s="1" t="inlineStr">
+      <c r="Q59" s="1" t="inlineStr">
         <is>
           <t>target_package_tip_retention_fraction</t>
         </is>
       </c>
-      <c r="R57" s="1" t="inlineStr">
+      <c r="R59" s="1" t="inlineStr">
         <is>
           <t>target_package_origin_partition_count</t>
         </is>
       </c>
-      <c r="S57" s="1" t="inlineStr">
+      <c r="S59" s="1" t="inlineStr">
         <is>
           <t>local_origin_consistency_status</t>
         </is>
       </c>
-      <c r="T57" s="1" t="inlineStr">
+      <c r="T59" s="1" t="inlineStr">
         <is>
           <t>preserves_single_origin_consistent_package</t>
         </is>
       </c>
-      <c r="U57" s="1" t="inlineStr">
+      <c r="U59" s="1" t="inlineStr">
         <is>
           <t>covering_local_origin_ids</t>
         </is>
       </c>
-      <c r="V57" s="1" t="inlineStr">
+      <c r="V59" s="1" t="inlineStr">
         <is>
           <t>covering_branch_supports</t>
         </is>
       </c>
-      <c r="W57" s="1" t="inlineStr">
+      <c r="W59" s="1" t="inlineStr">
         <is>
           <t>representative_covering_branch_support</t>
         </is>
       </c>
-      <c r="X57" s="1" t="inlineStr">
+      <c r="X59" s="1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="Y57" s="1" t="inlineStr">
+      <c r="Y59" s="1" t="inlineStr">
         <is>
           <t>status_detail</t>
         </is>
       </c>
-      <c r="Z57" s="1" t="inlineStr">
+      <c r="Z59" s="1" t="inlineStr">
         <is>
           <t>selection_plan</t>
         </is>
       </c>
-      <c r="AA57" s="1" t="inlineStr">
+      <c r="AA59" s="1" t="inlineStr">
         <is>
           <t>local_phylo_dir</t>
         </is>
       </c>
-      <c r="AB57" s="1" t="inlineStr">
+      <c r="AB59" s="1" t="inlineStr">
         <is>
           <t>local_asr_dir</t>
         </is>
       </c>
-      <c r="AC57" s="1" t="inlineStr">
+      <c r="AC59" s="1" t="inlineStr">
         <is>
           <t>notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>origin_0001</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>prn_evt_coding_disrupted_is481__is481__gap1043</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>FRA</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Q58" t="inlineStr">
-        <is>
-          <t>1.000000</t>
-        </is>
-      </c>
-      <c r="R58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>single_origin_consistent</t>
-        </is>
-      </c>
-      <c r="T58" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>origin_0001</t>
-        </is>
-      </c>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="W58" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Y58" t="inlineStr"/>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>pipelines/bp_step5/work/local_rooted_package_trees/origin_0001/snippy_ctg_plan.tsv</t>
-        </is>
-      </c>
-      <c r="AA58" t="inlineStr">
-        <is>
-          <t>outputs/workflow/local_rooted_package_trees/origin_0001/phylo</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>outputs/workflow/local_rooted_package_trees/origin_0001/asr</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>package_local_rooted_snp_tree_rebuilt_from_existing_snippy_outputs_then_passed_through_standard_m4_and_m5_wrappers</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>origin_0003</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>prn_evt_rearrangement__within_contig__cov58</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Q59" t="inlineStr">
-        <is>
-          <t>1.000000</t>
-        </is>
-      </c>
-      <c r="R59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>single_origin_consistent</t>
-        </is>
-      </c>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>origin_0001</t>
-        </is>
-      </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="W59" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Y59" t="inlineStr"/>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>pipelines/bp_step5/work/local_rooted_package_trees/origin_0003/snippy_ctg_plan.tsv</t>
-        </is>
-      </c>
-      <c r="AA59" t="inlineStr">
-        <is>
-          <t>outputs/workflow/local_rooted_package_trees/origin_0003/phylo</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>outputs/workflow/local_rooted_package_trees/origin_0003/asr</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>package_local_rooted_snp_tree_rebuilt_from_existing_snippy_outputs_then_passed_through_standard_m4_and_m5_wrappers</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>origin_0007</t>
+          <t>origin_0001</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -7326,7 +7376,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -7351,22 +7401,22 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>18</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -7376,12 +7426,12 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -7432,17 +7482,17 @@
       <c r="Y60" t="inlineStr"/>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>pipelines/bp_step5/work/local_rooted_package_trees/origin_0007/snippy_ctg_plan.tsv</t>
+          <t>pipelines/bp_step5/work/local_rooted_package_trees/origin_0001/snippy_ctg_plan.tsv</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>outputs/workflow/local_rooted_package_trees/origin_0007/phylo</t>
+          <t>outputs/workflow/local_rooted_package_trees/origin_0001/phylo</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>outputs/workflow/local_rooted_package_trees/origin_0007/asr</t>
+          <t>outputs/workflow/local_rooted_package_trees/origin_0001/asr</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
@@ -7454,112 +7504,108 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>origin_0008</t>
+          <t>origin_0003</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>prn_evt_coding_disrupted_is481__is481__gap1043</t>
+          <t>prn_evt_rearrangement__within_contig__cov58</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>0.157895</t>
+          <t>1.000000</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>split_across_multiple_local_origins</t>
+          <t>single_origin_consistent</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>origin_0001;origin_0003</t>
+          <t>origin_0001</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>NA;85</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="W61" t="inlineStr">
@@ -7575,20 +7621,306 @@
       <c r="Y61" t="inlineStr"/>
       <c r="Z61" t="inlineStr">
         <is>
+          <t>pipelines/bp_step5/work/local_rooted_package_trees/origin_0003/snippy_ctg_plan.tsv</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>outputs/workflow/local_rooted_package_trees/origin_0003/phylo</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>outputs/workflow/local_rooted_package_trees/origin_0003/asr</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>package_local_rooted_snp_tree_rebuilt_from_existing_snippy_outputs_then_passed_through_standard_m4_and_m5_wrappers</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>origin_0007</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>prn_evt_coding_disrupted_is481__is481__gap1043</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>1.000000</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>single_origin_consistent</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>origin_0001</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr"/>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>pipelines/bp_step5/work/local_rooted_package_trees/origin_0007/snippy_ctg_plan.tsv</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>outputs/workflow/local_rooted_package_trees/origin_0007/phylo</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>outputs/workflow/local_rooted_package_trees/origin_0007/asr</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>package_local_rooted_snp_tree_rebuilt_from_existing_snippy_outputs_then_passed_through_standard_m4_and_m5_wrappers</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>origin_0008</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>prn_evt_coding_disrupted_is481__is481__gap1043</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>0.157895</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>split_across_multiple_local_origins</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>origin_0001;origin_0003</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>NA;85</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr"/>
+      <c r="Z63" t="inlineStr">
+        <is>
           <t>pipelines/bp_step5/work/local_rooted_package_trees/origin_0008/snippy_ctg_plan.tsv</t>
         </is>
       </c>
-      <c r="AA61" t="inlineStr">
+      <c r="AA63" t="inlineStr">
         <is>
           <t>outputs/workflow/local_rooted_package_trees/origin_0008/phylo</t>
         </is>
       </c>
-      <c r="AB61" t="inlineStr">
+      <c r="AB63" t="inlineStr">
         <is>
           <t>outputs/workflow/local_rooted_package_trees/origin_0008/asr</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
+      <c r="AC63" t="inlineStr">
         <is>
           <t>package_local_rooted_snp_tree_rebuilt_from_existing_snippy_outputs_then_passed_through_standard_m4_and_m5_wrappers</t>
         </is>
@@ -7605,7 +7937,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU61"/>
+  <dimension ref="A1:AU63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -7832,12 +8164,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>prn_evt_insufficient__not_available_current_step3</t>
+          <t>prn_evt_fragmented_contigs</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>insufficient_data</t>
+          <t>uncertain_fragmented_assembly</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -8359,12 +8691,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>prn_evt_insufficient__not_available_current_step3</t>
+          <t>prn_evt_fragmented_contigs</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>insufficient_data</t>
+          <t>uncertain_fragmented_assembly</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -8651,7 +8983,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>319</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -8708,7 +9040,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>105</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -8765,7 +9097,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>58</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -8792,17 +9124,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>prn_evt_insufficient__not_available_current_step3</t>
+          <t>prn_evt_fragmented_contigs</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>insufficient_data</t>
+          <t>uncertain_fragmented_assembly</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -8876,7 +9208,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -8960,17 +9292,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>prn_evt_other_disruption__insertion_like__gap1040</t>
+          <t>prn_evt_insufficient__partial</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>coding_disrupted_other</t>
+          <t>insufficient_data</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -8997,12 +9329,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>prn_evt_rearrangement__within_contig__cov94</t>
+          <t>prn_evt_other_disruption__insertion_like__gap1040</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>coding_disrupted_inversion_or_rearrangement</t>
+          <t>coding_disrupted_other</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -9026,435 +9358,311 @@
         </is>
       </c>
     </row>
-    <row r="39"/>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>prn_evt_rearrangement__within_contig__cov66</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>coding_disrupted_inversion_or_rearrangement</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
     <row r="40"/>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr">
+    <row r="41"/>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
         <is>
           <t>source_file</t>
         </is>
       </c>
-      <c r="B41" s="1" t="inlineStr">
+      <c r="B42" s="1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t>manuscript/figure_data/selected_country/selected_country_origin_package_summary.tsv</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>found</t>
         </is>
       </c>
     </row>
-    <row r="43"/>
-    <row r="44">
-      <c r="A44" s="1" t="inlineStr">
+    <row r="44"/>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
         <is>
           <t>origin_id</t>
         </is>
       </c>
-      <c r="B44" s="1" t="inlineStr">
+      <c r="B45" s="1" t="inlineStr">
         <is>
           <t>analysis_source</t>
         </is>
       </c>
-      <c r="C44" s="1" t="inlineStr">
+      <c r="C45" s="1" t="inlineStr">
         <is>
           <t>n_disrupted_descendants</t>
         </is>
       </c>
-      <c r="D44" s="1" t="inlineStr">
+      <c r="D45" s="1" t="inlineStr">
         <is>
           <t>n_total_descendants</t>
         </is>
       </c>
-      <c r="E44" s="1" t="inlineStr">
+      <c r="E45" s="1" t="inlineStr">
         <is>
           <t>follow_up_years</t>
         </is>
       </c>
-      <c r="F44" s="1" t="inlineStr">
+      <c r="F45" s="1" t="inlineStr">
         <is>
           <t>origin_country_iso3</t>
         </is>
       </c>
-      <c r="G44" s="1" t="inlineStr">
+      <c r="G45" s="1" t="inlineStr">
         <is>
           <t>origin_year</t>
         </is>
       </c>
-      <c r="H44" s="1" t="inlineStr">
+      <c r="H45" s="1" t="inlineStr">
         <is>
           <t>last_year</t>
         </is>
       </c>
-      <c r="I44" s="1" t="inlineStr">
+      <c r="I45" s="1" t="inlineStr">
         <is>
           <t>mechanism_group</t>
         </is>
       </c>
-      <c r="J44" s="1" t="inlineStr">
+      <c r="J45" s="1" t="inlineStr">
         <is>
           <t>origin_ptxP_allele</t>
         </is>
       </c>
-      <c r="K44" s="1" t="inlineStr">
+      <c r="K45" s="1" t="inlineStr">
         <is>
           <t>origin_fim2_hash</t>
         </is>
       </c>
-      <c r="L44" s="1" t="inlineStr">
+      <c r="L45" s="1" t="inlineStr">
         <is>
           <t>origin_fim3_hash</t>
         </is>
       </c>
-      <c r="M44" s="1" t="inlineStr">
+      <c r="M45" s="1" t="inlineStr">
         <is>
           <t>origin_genotype_background</t>
         </is>
       </c>
-      <c r="N44" s="1" t="inlineStr">
+      <c r="N45" s="1" t="inlineStr">
         <is>
           <t>major_lineage</t>
         </is>
       </c>
-      <c r="O44" s="1" t="inlineStr">
+      <c r="O45" s="1" t="inlineStr">
         <is>
           <t>major_lineage_source</t>
         </is>
       </c>
-      <c r="P44" s="1" t="inlineStr">
+      <c r="P45" s="1" t="inlineStr">
         <is>
           <t>major_mlst_st</t>
         </is>
       </c>
-      <c r="Q44" s="1" t="inlineStr">
+      <c r="Q45" s="1" t="inlineStr">
         <is>
           <t>major_background_profile_id</t>
         </is>
       </c>
-      <c r="R44" s="1" t="inlineStr">
+      <c r="R45" s="1" t="inlineStr">
         <is>
           <t>major_background_label</t>
         </is>
       </c>
-      <c r="S44" s="1" t="inlineStr">
+      <c r="S45" s="1" t="inlineStr">
         <is>
           <t>major_ptxP_label</t>
         </is>
       </c>
-      <c r="T44" s="1" t="inlineStr">
+      <c r="T45" s="1" t="inlineStr">
         <is>
           <t>major_fim3_label</t>
         </is>
       </c>
-      <c r="U44" s="1" t="inlineStr">
+      <c r="U45" s="1" t="inlineStr">
         <is>
           <t>major_fhaB2400_5550_label</t>
         </is>
       </c>
-      <c r="V44" s="1" t="inlineStr">
+      <c r="V45" s="1" t="inlineStr">
         <is>
           <t>major_23s_status</t>
         </is>
       </c>
-      <c r="W44" s="1" t="inlineStr">
+      <c r="W45" s="1" t="inlineStr">
         <is>
           <t>macrolide_background</t>
         </is>
       </c>
-      <c r="X44" s="1" t="inlineStr">
+      <c r="X45" s="1" t="inlineStr">
         <is>
           <t>vaccine_environment</t>
         </is>
       </c>
-      <c r="Y44" s="1" t="inlineStr">
+      <c r="Y45" s="1" t="inlineStr">
         <is>
           <t>branch_support</t>
         </is>
       </c>
-      <c r="Z44" s="1" t="inlineStr">
+      <c r="Z45" s="1" t="inlineStr">
         <is>
           <t>origin_support_score</t>
         </is>
       </c>
-      <c r="AA44" s="1" t="inlineStr">
+      <c r="AA45" s="1" t="inlineStr">
         <is>
           <t>origin_confidence</t>
         </is>
       </c>
-      <c r="AB44" s="1" t="inlineStr">
+      <c r="AB45" s="1" t="inlineStr">
         <is>
           <t>established_ge3_descendants</t>
         </is>
       </c>
-      <c r="AC44" s="1" t="inlineStr">
+      <c r="AC45" s="1" t="inlineStr">
         <is>
           <t>established_ge2_followup_years</t>
         </is>
       </c>
-      <c r="AD44" s="1" t="inlineStr">
+      <c r="AD45" s="1" t="inlineStr">
         <is>
           <t>dominant_prn_mechanism</t>
         </is>
       </c>
-      <c r="AE44" s="1" t="inlineStr">
+      <c r="AE45" s="1" t="inlineStr">
         <is>
           <t>pastml_support_consistent</t>
         </is>
       </c>
-      <c r="AF44" s="1" t="inlineStr">
+      <c r="AF45" s="1" t="inlineStr">
         <is>
           <t>origin_ptxP_like</t>
         </is>
       </c>
-      <c r="AG44" s="1" t="inlineStr">
+      <c r="AG45" s="1" t="inlineStr">
         <is>
           <t>origin_fim2_present</t>
         </is>
       </c>
-      <c r="AH44" s="1" t="inlineStr">
+      <c r="AH45" s="1" t="inlineStr">
         <is>
           <t>origin_fim3_present</t>
         </is>
       </c>
-      <c r="AI44" s="1" t="inlineStr">
+      <c r="AI45" s="1" t="inlineStr">
         <is>
           <t>origin_mr_dominant</t>
         </is>
       </c>
-      <c r="AJ44" s="1" t="inlineStr">
+      <c r="AJ45" s="1" t="inlineStr">
         <is>
           <t>combined_hitchhiker_signature</t>
         </is>
       </c>
-      <c r="AK44" s="1" t="inlineStr">
+      <c r="AK45" s="1" t="inlineStr">
         <is>
           <t>background_signature</t>
         </is>
       </c>
-      <c r="AL44" s="1" t="inlineStr">
+      <c r="AL45" s="1" t="inlineStr">
         <is>
           <t>package_country_iso3</t>
         </is>
       </c>
-      <c r="AM44" s="1" t="inlineStr">
+      <c r="AM45" s="1" t="inlineStr">
         <is>
           <t>local_origin_consistency_status</t>
         </is>
       </c>
-      <c r="AN44" s="1" t="inlineStr">
+      <c r="AN45" s="1" t="inlineStr">
         <is>
           <t>preserves_single_origin_consistent_package</t>
         </is>
       </c>
-      <c r="AO44" s="1" t="inlineStr">
+      <c r="AO45" s="1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="AP44" s="1" t="inlineStr">
+      <c r="AP45" s="1" t="inlineStr">
         <is>
           <t>tree_representative_validation_level</t>
         </is>
       </c>
-      <c r="AQ44" s="1" t="inlineStr">
+      <c r="AQ45" s="1" t="inlineStr">
         <is>
           <t>representative_validation_level</t>
         </is>
       </c>
-      <c r="AR44" s="1" t="inlineStr">
+      <c r="AR45" s="1" t="inlineStr">
         <is>
           <t>origin_package_hard_anchor</t>
         </is>
       </c>
-      <c r="AS44" s="1" t="inlineStr">
+      <c r="AS45" s="1" t="inlineStr">
         <is>
           <t>dominant_event_hard_anchor</t>
         </is>
       </c>
-      <c r="AT44" s="1" t="inlineStr">
+      <c r="AT45" s="1" t="inlineStr">
         <is>
           <t>dominant_prn_event_id</t>
         </is>
       </c>
-      <c r="AU44" s="1" t="inlineStr">
+      <c r="AU45" s="1" t="inlineStr">
         <is>
           <t>dominant_event_validation_level</t>
         </is>
       </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>origin_0019</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>support_filtered_fitch</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>NZL</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>2012.0</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>2017.0</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>IS481</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>ptxP_3</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>f42558239a68e014b1b3707b0dfb5fd2</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>f42558239a68e014b1b3707b0dfb5fd2</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>ptxP3/PRN-</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="inlineStr"/>
-      <c r="S45" t="inlineStr"/>
-      <c r="T45" t="inlineStr"/>
-      <c r="U45" t="inlineStr"/>
-      <c r="V45" t="inlineStr"/>
-      <c r="W45" t="inlineStr">
-        <is>
-          <t>not_MR_A2047G_dominant</t>
-        </is>
-      </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>routine_ap_prn_positive</t>
-        </is>
-      </c>
-      <c r="Y45" t="inlineStr">
-        <is>
-          <t>98.0</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AA45" t="inlineStr"/>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD45" t="inlineStr">
-        <is>
-          <t>coding_disrupted_is481</t>
-        </is>
-      </c>
-      <c r="AE45" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AF45" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AG45" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>ptxP3|fim3_present|fhaB2400_5550_unassigned|not_MR_A2047G_dominant|routine_ap_prn_positive</t>
-        </is>
-      </c>
-      <c r="AL45" t="inlineStr"/>
-      <c r="AM45" t="inlineStr"/>
-      <c r="AN45" t="inlineStr"/>
-      <c r="AO45" t="inlineStr"/>
-      <c r="AP45" t="inlineStr"/>
-      <c r="AQ45" t="inlineStr"/>
-      <c r="AR45" t="inlineStr"/>
-      <c r="AS45" t="inlineStr"/>
-      <c r="AT45" t="inlineStr"/>
-      <c r="AU45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>origin_0020</t>
+          <t>origin_0019</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -9519,11 +9727,7 @@
       </c>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr"/>
@@ -9542,7 +9746,7 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
@@ -9615,7 +9819,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>origin_0018</t>
+          <t>origin_0020</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -9625,32 +9829,32 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>NZL</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2010.0</t>
+          <t>2012.0</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2020.0</t>
+          <t>2017.0</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -9680,11 +9884,7 @@
       </c>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr"/>
@@ -9703,12 +9903,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>0.96904</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr"/>
@@ -9776,7 +9976,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>origin_0015</t>
+          <t>origin_0018</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -9786,17 +9986,17 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>322</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>323</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -9806,12 +10006,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2011.0</t>
+          <t>2010.0</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2019.0</t>
+          <t>2020.0</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -9841,11 +10041,7 @@
       </c>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr"/>
@@ -9864,12 +10060,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>0.975</t>
+          <t>0.944272</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr"/>
@@ -9937,7 +10133,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>origin_0002</t>
+          <t>origin_0013</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -9947,17 +10143,17 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -9967,12 +10163,12 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2012.0</t>
+          <t>2011.0</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2018.0</t>
+          <t>2014.0</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -10002,11 +10198,7 @@
       </c>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr"/>
@@ -10030,7 +10222,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.833333</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr"/>
@@ -10088,41 +10280,17 @@
       <c r="AM49" t="inlineStr"/>
       <c r="AN49" t="inlineStr"/>
       <c r="AO49" t="inlineStr"/>
-      <c r="AP49" t="inlineStr">
-        <is>
-          <t>read_backed_supported</t>
-        </is>
-      </c>
-      <c r="AQ49" t="inlineStr">
-        <is>
-          <t>read_backed_supported</t>
-        </is>
-      </c>
-      <c r="AR49" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AS49" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AT49" t="inlineStr">
-        <is>
-          <t>prn_evt_rearrangement__within_contig__cov58</t>
-        </is>
-      </c>
-      <c r="AU49" t="inlineStr">
-        <is>
-          <t>read_backed_supported</t>
-        </is>
-      </c>
+      <c r="AP49" t="inlineStr"/>
+      <c r="AQ49" t="inlineStr"/>
+      <c r="AR49" t="inlineStr"/>
+      <c r="AS49" t="inlineStr"/>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AU49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>origin_0011</t>
+          <t>origin_0015</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -10132,17 +10300,17 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>39</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -10152,17 +10320,17 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2015.0</t>
+          <t>2011.0</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2020.0</t>
+          <t>2019.0</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>inversion/rearrangement</t>
+          <t>IS481</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -10187,11 +10355,7 @@
       </c>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr"/>
@@ -10210,12 +10374,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>0.881356</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr"/>
@@ -10231,7 +10395,7 @@
       </c>
       <c r="AD50" t="inlineStr">
         <is>
-          <t>coding_disrupted_inversion_or_rearrangement</t>
+          <t>coding_disrupted_is481</t>
         </is>
       </c>
       <c r="AE50" t="inlineStr">
@@ -10283,7 +10447,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>origin_0005</t>
+          <t>origin_0002</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -10293,17 +10457,17 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -10313,12 +10477,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2016.0</t>
+          <t>2012.0</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2016.0</t>
+          <t>2018.0</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -10348,11 +10512,7 @@
       </c>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr"/>
@@ -10382,12 +10542,12 @@
       <c r="AA51" t="inlineStr"/>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD51" t="inlineStr">
@@ -10434,473 +10594,529 @@
       <c r="AM51" t="inlineStr"/>
       <c r="AN51" t="inlineStr"/>
       <c r="AO51" t="inlineStr"/>
-      <c r="AP51" t="inlineStr"/>
-      <c r="AQ51" t="inlineStr"/>
-      <c r="AR51" t="inlineStr"/>
-      <c r="AS51" t="inlineStr"/>
-      <c r="AT51" t="inlineStr"/>
-      <c r="AU51" t="inlineStr"/>
-    </row>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54">
-      <c r="A54" s="1" t="inlineStr">
+      <c r="AP51" t="inlineStr">
+        <is>
+          <t>read_backed_supported</t>
+        </is>
+      </c>
+      <c r="AQ51" t="inlineStr">
+        <is>
+          <t>read_backed_supported</t>
+        </is>
+      </c>
+      <c r="AR51" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AS51" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AT51" t="inlineStr">
+        <is>
+          <t>prn_evt_rearrangement__within_contig__cov58</t>
+        </is>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
+          <t>read_backed_supported</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>origin_0010</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>support_filtered_fitch</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2015.0</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>2020.0</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>inversion/rearrangement</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>ptxP_3</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>f42558239a68e014b1b3707b0dfb5fd2</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>f42558239a68e014b1b3707b0dfb5fd2</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>ptxP3/PRN-</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>not_MR_A2047G_dominant</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>routine_ap_prn_positive</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>0.881356</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr"/>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD52" t="inlineStr">
+        <is>
+          <t>coding_disrupted_inversion_or_rearrangement</t>
+        </is>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AG52" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>ptxP3|fim3_present|fhaB2400_5550_unassigned|not_MR_A2047G_dominant|routine_ap_prn_positive</t>
+        </is>
+      </c>
+      <c r="AL52" t="inlineStr"/>
+      <c r="AM52" t="inlineStr"/>
+      <c r="AN52" t="inlineStr"/>
+      <c r="AO52" t="inlineStr"/>
+      <c r="AP52" t="inlineStr"/>
+      <c r="AQ52" t="inlineStr"/>
+      <c r="AR52" t="inlineStr"/>
+      <c r="AS52" t="inlineStr"/>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AU52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>origin_0005</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>support_filtered_fitch</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2016.0</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>2016.0</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>inversion/rearrangement</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>ptxP_3</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>f42558239a68e014b1b3707b0dfb5fd2</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>f42558239a68e014b1b3707b0dfb5fd2</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>ptxP3/PRN-</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="inlineStr"/>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr"/>
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>not_MR_A2047G_dominant</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>routine_ap_prn_positive</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr"/>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD53" t="inlineStr">
+        <is>
+          <t>coding_disrupted_inversion_or_rearrangement</t>
+        </is>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AG53" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>ptxP3|fim3_present|fhaB2400_5550_unassigned|not_MR_A2047G_dominant|routine_ap_prn_positive</t>
+        </is>
+      </c>
+      <c r="AL53" t="inlineStr"/>
+      <c r="AM53" t="inlineStr"/>
+      <c r="AN53" t="inlineStr"/>
+      <c r="AO53" t="inlineStr"/>
+      <c r="AP53" t="inlineStr"/>
+      <c r="AQ53" t="inlineStr"/>
+      <c r="AR53" t="inlineStr"/>
+      <c r="AS53" t="inlineStr"/>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AU53" t="inlineStr"/>
+    </row>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
         <is>
           <t>source_file</t>
         </is>
       </c>
-      <c r="B54" s="1" t="inlineStr">
+      <c r="B56" s="1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
+    <row r="57">
+      <c r="A57" t="inlineStr">
         <is>
           <t>manuscript/figure_data/local_rooted_package_tree_summary.tsv</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>found</t>
         </is>
       </c>
     </row>
-    <row r="56"/>
-    <row r="57">
-      <c r="A57" s="1" t="inlineStr">
+    <row r="58"/>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr">
         <is>
           <t>origin_id</t>
         </is>
       </c>
-      <c r="B57" s="1" t="inlineStr">
+      <c r="B59" s="1" t="inlineStr">
         <is>
           <t>dominant_prn_event_id</t>
         </is>
       </c>
-      <c r="C57" s="1" t="inlineStr">
+      <c r="C59" s="1" t="inlineStr">
         <is>
           <t>major_mlst_st</t>
         </is>
       </c>
-      <c r="D57" s="1" t="inlineStr">
+      <c r="D59" s="1" t="inlineStr">
         <is>
           <t>package_country_iso3</t>
         </is>
       </c>
-      <c r="E57" s="1" t="inlineStr">
+      <c r="E59" s="1" t="inlineStr">
         <is>
           <t>package_target_disrupted_tips</t>
         </is>
       </c>
-      <c r="F57" s="1" t="inlineStr">
+      <c r="F59" s="1" t="inlineStr">
         <is>
           <t>rooted_tree_selected_targets</t>
         </is>
       </c>
-      <c r="G57" s="1" t="inlineStr">
+      <c r="G59" s="1" t="inlineStr">
         <is>
           <t>rooted_tree_selected_intact_neighbors</t>
         </is>
       </c>
-      <c r="H57" s="1" t="inlineStr">
+      <c r="H59" s="1" t="inlineStr">
         <is>
           <t>proxy_extra_disrupted_targets_selected</t>
         </is>
       </c>
-      <c r="I57" s="1" t="inlineStr">
+      <c r="I59" s="1" t="inlineStr">
         <is>
           <t>proxy_selected_intact_neighbors</t>
         </is>
       </c>
-      <c r="J57" s="1" t="inlineStr">
+      <c r="J59" s="1" t="inlineStr">
         <is>
           <t>selected_total_genomes</t>
         </is>
       </c>
-      <c r="K57" s="1" t="inlineStr">
+      <c r="K59" s="1" t="inlineStr">
         <is>
           <t>completed_snippy_genomes</t>
         </is>
       </c>
-      <c r="L57" s="1" t="inlineStr">
+      <c r="L59" s="1" t="inlineStr">
         <is>
           <t>local_tip_count</t>
         </is>
       </c>
-      <c r="M57" s="1" t="inlineStr">
+      <c r="M59" s="1" t="inlineStr">
         <is>
           <t>local_disrupted_tip_count</t>
         </is>
       </c>
-      <c r="N57" s="1" t="inlineStr">
+      <c r="N59" s="1" t="inlineStr">
         <is>
           <t>local_fitch_origin_events</t>
         </is>
       </c>
-      <c r="O57" s="1" t="inlineStr">
+      <c r="O59" s="1" t="inlineStr">
         <is>
           <t>local_pastml_origin_events</t>
         </is>
       </c>
-      <c r="P57" s="1" t="inlineStr">
+      <c r="P59" s="1" t="inlineStr">
         <is>
           <t>target_package_retained_disrupted_tips</t>
         </is>
       </c>
-      <c r="Q57" s="1" t="inlineStr">
+      <c r="Q59" s="1" t="inlineStr">
         <is>
           <t>target_package_tip_retention_fraction</t>
         </is>
       </c>
-      <c r="R57" s="1" t="inlineStr">
+      <c r="R59" s="1" t="inlineStr">
         <is>
           <t>target_package_origin_partition_count</t>
         </is>
       </c>
-      <c r="S57" s="1" t="inlineStr">
+      <c r="S59" s="1" t="inlineStr">
         <is>
           <t>local_origin_consistency_status</t>
         </is>
       </c>
-      <c r="T57" s="1" t="inlineStr">
+      <c r="T59" s="1" t="inlineStr">
         <is>
           <t>preserves_single_origin_consistent_package</t>
         </is>
       </c>
-      <c r="U57" s="1" t="inlineStr">
+      <c r="U59" s="1" t="inlineStr">
         <is>
           <t>covering_local_origin_ids</t>
         </is>
       </c>
-      <c r="V57" s="1" t="inlineStr">
+      <c r="V59" s="1" t="inlineStr">
         <is>
           <t>covering_branch_supports</t>
         </is>
       </c>
-      <c r="W57" s="1" t="inlineStr">
+      <c r="W59" s="1" t="inlineStr">
         <is>
           <t>representative_covering_branch_support</t>
         </is>
       </c>
-      <c r="X57" s="1" t="inlineStr">
+      <c r="X59" s="1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="Y57" s="1" t="inlineStr">
+      <c r="Y59" s="1" t="inlineStr">
         <is>
           <t>status_detail</t>
         </is>
       </c>
-      <c r="Z57" s="1" t="inlineStr">
+      <c r="Z59" s="1" t="inlineStr">
         <is>
           <t>selection_plan</t>
         </is>
       </c>
-      <c r="AA57" s="1" t="inlineStr">
+      <c r="AA59" s="1" t="inlineStr">
         <is>
           <t>local_phylo_dir</t>
         </is>
       </c>
-      <c r="AB57" s="1" t="inlineStr">
+      <c r="AB59" s="1" t="inlineStr">
         <is>
           <t>local_asr_dir</t>
         </is>
       </c>
-      <c r="AC57" s="1" t="inlineStr">
+      <c r="AC59" s="1" t="inlineStr">
         <is>
           <t>notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>origin_0001</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>prn_evt_coding_disrupted_is481__is481__gap1043</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>FRA</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Q58" t="inlineStr">
-        <is>
-          <t>1.000000</t>
-        </is>
-      </c>
-      <c r="R58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>single_origin_consistent</t>
-        </is>
-      </c>
-      <c r="T58" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>origin_0001</t>
-        </is>
-      </c>
-      <c r="V58" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="W58" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Y58" t="inlineStr"/>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>pipelines/bp_step5/work/local_rooted_package_trees/origin_0001/snippy_ctg_plan.tsv</t>
-        </is>
-      </c>
-      <c r="AA58" t="inlineStr">
-        <is>
-          <t>outputs/workflow/local_rooted_package_trees/origin_0001/phylo</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>outputs/workflow/local_rooted_package_trees/origin_0001/asr</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>package_local_rooted_snp_tree_rebuilt_from_existing_snippy_outputs_then_passed_through_standard_m4_and_m5_wrappers</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>origin_0003</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>prn_evt_rearrangement__within_contig__cov58</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Q59" t="inlineStr">
-        <is>
-          <t>1.000000</t>
-        </is>
-      </c>
-      <c r="R59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>single_origin_consistent</t>
-        </is>
-      </c>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>origin_0001</t>
-        </is>
-      </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="W59" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="Y59" t="inlineStr"/>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>pipelines/bp_step5/work/local_rooted_package_trees/origin_0003/snippy_ctg_plan.tsv</t>
-        </is>
-      </c>
-      <c r="AA59" t="inlineStr">
-        <is>
-          <t>outputs/workflow/local_rooted_package_trees/origin_0003/phylo</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>outputs/workflow/local_rooted_package_trees/origin_0003/asr</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>package_local_rooted_snp_tree_rebuilt_from_existing_snippy_outputs_then_passed_through_standard_m4_and_m5_wrappers</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>origin_0007</t>
+          <t>origin_0001</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -10915,7 +11131,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -10940,22 +11156,22 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>18</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>19</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -10965,12 +11181,12 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -11021,17 +11237,17 @@
       <c r="Y60" t="inlineStr"/>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>pipelines/bp_step5/work/local_rooted_package_trees/origin_0007/snippy_ctg_plan.tsv</t>
+          <t>pipelines/bp_step5/work/local_rooted_package_trees/origin_0001/snippy_ctg_plan.tsv</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>outputs/workflow/local_rooted_package_trees/origin_0007/phylo</t>
+          <t>outputs/workflow/local_rooted_package_trees/origin_0001/phylo</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>outputs/workflow/local_rooted_package_trees/origin_0007/asr</t>
+          <t>outputs/workflow/local_rooted_package_trees/origin_0001/asr</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
@@ -11043,112 +11259,108 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>origin_0008</t>
+          <t>origin_0003</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>prn_evt_coding_disrupted_is481__is481__gap1043</t>
+          <t>prn_evt_rearrangement__within_contig__cov58</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>0.157895</t>
+          <t>1.000000</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>split_across_multiple_local_origins</t>
+          <t>single_origin_consistent</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>origin_0001;origin_0003</t>
+          <t>origin_0001</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>NA;85</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="W61" t="inlineStr">
@@ -11164,20 +11376,306 @@
       <c r="Y61" t="inlineStr"/>
       <c r="Z61" t="inlineStr">
         <is>
+          <t>pipelines/bp_step5/work/local_rooted_package_trees/origin_0003/snippy_ctg_plan.tsv</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>outputs/workflow/local_rooted_package_trees/origin_0003/phylo</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>outputs/workflow/local_rooted_package_trees/origin_0003/asr</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>package_local_rooted_snp_tree_rebuilt_from_existing_snippy_outputs_then_passed_through_standard_m4_and_m5_wrappers</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>origin_0007</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>prn_evt_coding_disrupted_is481__is481__gap1043</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>1.000000</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>single_origin_consistent</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>origin_0001</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr"/>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>pipelines/bp_step5/work/local_rooted_package_trees/origin_0007/snippy_ctg_plan.tsv</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>outputs/workflow/local_rooted_package_trees/origin_0007/phylo</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>outputs/workflow/local_rooted_package_trees/origin_0007/asr</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>package_local_rooted_snp_tree_rebuilt_from_existing_snippy_outputs_then_passed_through_standard_m4_and_m5_wrappers</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>origin_0008</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>prn_evt_coding_disrupted_is481__is481__gap1043</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>0.157895</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>split_across_multiple_local_origins</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>origin_0001;origin_0003</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>NA;85</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr"/>
+      <c r="Z63" t="inlineStr">
+        <is>
           <t>pipelines/bp_step5/work/local_rooted_package_trees/origin_0008/snippy_ctg_plan.tsv</t>
         </is>
       </c>
-      <c r="AA61" t="inlineStr">
+      <c r="AA63" t="inlineStr">
         <is>
           <t>outputs/workflow/local_rooted_package_trees/origin_0008/phylo</t>
         </is>
       </c>
-      <c r="AB61" t="inlineStr">
+      <c r="AB63" t="inlineStr">
         <is>
           <t>outputs/workflow/local_rooted_package_trees/origin_0008/asr</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
+      <c r="AC63" t="inlineStr">
         <is>
           <t>package_local_rooted_snp_tree_rebuilt_from_existing_snippy_outputs_then_passed_through_standard_m4_and_m5_wrappers</t>
         </is>
